--- a/Profit.xlsx
+++ b/Profit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COPILOTO_PRICE_ACTION_AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D489723C-E0B0-4831-91CB-2C89C2685279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F8EAEC-DC79-4F67-B5B2-ACD7880B14E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" xr2:uid="{053FB8ED-3EE0-40A4-8A34-98C4171923B1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="24090" windowHeight="13020" xr2:uid="{053FB8ED-3EE0-40A4-8A34-98C4171923B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Asset</t>
   </si>
@@ -69,13 +69,10 @@
     <t>MACD Histograma</t>
   </si>
   <si>
-    <t>Média Móvel</t>
-  </si>
-  <si>
-    <t>WDOQ26</t>
-  </si>
-  <si>
-    <t>WINQ26</t>
+    <t>WINV26</t>
+  </si>
+  <si>
+    <t>Volume</t>
   </si>
 </sst>
 </file>
@@ -135,185 +132,94 @@
   <ddeLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ddeService="profitchart" ddeTopic="cot">
     <ddeItems>
       <ddeItem name="StdDocumentName" ole="1" advise="1"/>
-      <ddeItem name="WDOQ26.22" advise="1">
+      <ddeItem name="WINV26.22" advise="1">
         <values>
           <value t="str">
-            <val>41,98</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.3" advise="1">
+            <val>63,20</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.6" advise="1">
         <values>
           <value t="str">
-            <val>5.097,05</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.6" advise="1">
+            <val>-1.207,95 / -1.207,95</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.ABE" advise="1">
+        <values>
+          <value>
+            <val>171100</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.DAT" advise="1">
         <values>
           <value t="str">
-            <val>-2,81 / -2,81</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.ABE" advise="1">
-        <values>
-          <value>
-            <val>5077</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.DAT" advise="1">
-        <values>
-          <value t="str">
-            <val>31/07/2026</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.HOR" advise="1">
-        <values>
-          <value t="str">
-            <val>18:23:50</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.MAX" advise="1">
-        <values>
-          <value>
-            <val>5079.5</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.MED" advise="1">
-        <values>
-          <value>
-            <val>5077.5253265552692</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.MIN" advise="1">
-        <values>
-          <value>
-            <val>5075</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.NEG" advise="1">
-        <values>
-          <value>
-            <val>6103</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.PEX" advise="1">
-        <values>
-          <value>
-            <val>0</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.ULT" advise="1">
-        <values>
-          <value>
-            <val>5078</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WDOQ26.VEN" advise="1">
-        <values>
-          <value t="str">
-            <val>03/08/2026</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.22" advise="1">
-        <values>
-          <value t="str">
-            <val>37,63</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.3" advise="1">
-        <values>
-          <value t="str">
-            <val>176.547,50</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.6" advise="1">
-        <values>
-          <value t="str">
-            <val>251,33 / 251,33</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.ABE" advise="1">
-        <values>
-          <value>
-            <val>177470</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.DAT" advise="1">
-        <values>
-          <value t="str">
-            <val>31/07/2026</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.HOR" advise="1">
+            <val>14/08/2026</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.HOR" advise="1">
         <values>
           <value t="str">
             <val>18:24:59</val>
           </value>
         </values>
       </ddeItem>
-      <ddeItem name="WINQ26.MAX" advise="1">
-        <values>
-          <value>
-            <val>179495</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.MED" advise="1">
-        <values>
-          <value>
-            <val>178851.89070106987</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.MIN" advise="1">
-        <values>
-          <value>
-            <val>176985</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.NEG" advise="1">
-        <values>
-          <value>
-            <val>2489616</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.PEX" advise="1">
+      <ddeItem name="WINV26.MAX" advise="1">
+        <values>
+          <value>
+            <val>171240</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.MED" advise="1">
+        <values>
+          <value>
+            <val>169158.52895226577</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.MIN" advise="1">
+        <values>
+          <value>
+            <val>167975</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.NEG" advise="1">
+        <values>
+          <value>
+            <val>4751555</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.PEX" advise="1">
         <values>
           <value>
             <val>0</val>
           </value>
         </values>
       </ddeItem>
-      <ddeItem name="WINQ26.ULT" advise="1">
-        <values>
-          <value>
-            <val>178615</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WINQ26.VEN" advise="1">
+      <ddeItem name="WINV26.ULT" advise="1">
+        <values>
+          <value>
+            <val>170000</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.VEN" advise="1">
         <values>
           <value t="str">
-            <val>12/08/2026</val>
+            <val>14/10/2026</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="WINV26.VOL" advise="1">
+        <values>
+          <value>
+            <val>560326056711</val>
           </value>
         </values>
       </ddeItem>
@@ -619,8 +525,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9D09D2-3F42-4A00-8BF9-FD2B7B5A3F3B}">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -654,130 +570,73 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="str">
-        <f>[1]!WDOQ26.DAT</f>
-        <v>31/07/2026</v>
+        <f>[1]!WINV26.DAT</f>
+        <v>14/08/2026</v>
       </c>
       <c r="C2" t="str">
-        <f>[1]!WDOQ26.HOR</f>
-        <v>18:23:50</v>
+        <f>[1]!WINV26.HOR</f>
+        <v>18:24:59</v>
       </c>
       <c r="D2">
-        <f>[1]!WDOQ26.ULT</f>
-        <v>5078</v>
+        <f>[1]!WINV26.ULT</f>
+        <v>170000</v>
       </c>
       <c r="E2">
-        <f>[1]!WDOQ26.ABE</f>
-        <v>5077</v>
+        <f>[1]!WINV26.ABE</f>
+        <v>171100</v>
       </c>
       <c r="F2">
-        <f>[1]!WDOQ26.MAX</f>
-        <v>5079.5</v>
+        <f>[1]!WINV26.MAX</f>
+        <v>171240</v>
       </c>
       <c r="G2">
-        <f>[1]!WDOQ26.MIN</f>
-        <v>5075</v>
+        <f>[1]!WINV26.MIN</f>
+        <v>167975</v>
       </c>
       <c r="H2">
-        <f>[1]!WDOQ26.PEX</f>
+        <f>[1]!WINV26.PEX</f>
         <v>0</v>
       </c>
       <c r="I2">
-        <f>[1]!WDOQ26.MED</f>
-        <v>5077.5253265552692</v>
+        <f>[1]!WINV26.MED</f>
+        <v>169158.52895226577</v>
       </c>
       <c r="J2">
-        <f>[1]!WDOQ26.NEG</f>
-        <v>6103</v>
-      </c>
-      <c r="K2" t="str">
-        <f>[1]!WDOQ26.VEN</f>
-        <v>03/08/2026</v>
+        <f>[1]!WINV26.NEG</f>
+        <v>4751555</v>
+      </c>
+      <c r="K2">
+        <f>[1]!WINV26.VOL</f>
+        <v>560326056711</v>
       </c>
       <c r="L2" t="str">
-        <f>[1]!WDOQ26.22</f>
-        <v>41,98</v>
+        <f>[1]!WINV26.VEN</f>
+        <v>14/10/2026</v>
       </c>
       <c r="M2" t="str">
-        <f>[1]!WDOQ26.6</f>
-        <v>-2,81 / -2,81</v>
+        <f>[1]!WINV26.22</f>
+        <v>63,20</v>
       </c>
       <c r="N2" t="str">
-        <f>[1]!WDOQ26.3</f>
-        <v>5.097,05</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="str">
-        <f>[1]!WINQ26.DAT</f>
-        <v>31/07/2026</v>
-      </c>
-      <c r="C3" t="str">
-        <f>[1]!WINQ26.HOR</f>
-        <v>18:24:59</v>
-      </c>
-      <c r="D3">
-        <f>[1]!WINQ26.ULT</f>
-        <v>178615</v>
-      </c>
-      <c r="E3">
-        <f>[1]!WINQ26.ABE</f>
-        <v>177470</v>
-      </c>
-      <c r="F3">
-        <f>[1]!WINQ26.MAX</f>
-        <v>179495</v>
-      </c>
-      <c r="G3">
-        <f>[1]!WINQ26.MIN</f>
-        <v>176985</v>
-      </c>
-      <c r="H3">
-        <f>[1]!WINQ26.PEX</f>
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <f>[1]!WINQ26.MED</f>
-        <v>178851.89070106987</v>
-      </c>
-      <c r="J3">
-        <f>[1]!WINQ26.NEG</f>
-        <v>2489616</v>
-      </c>
-      <c r="K3" t="str">
-        <f>[1]!WINQ26.VEN</f>
-        <v>12/08/2026</v>
-      </c>
-      <c r="L3" t="str">
-        <f>[1]!WINQ26.22</f>
-        <v>37,63</v>
-      </c>
-      <c r="M3" t="str">
-        <f>[1]!WINQ26.6</f>
-        <v>251,33 / 251,33</v>
-      </c>
-      <c r="N3" t="str">
-        <f>[1]!WINQ26.3</f>
-        <v>176.547,50</v>
+        <f>[1]!WINV26.6</f>
+        <v>-1.207,95 / -1.207,95</v>
       </c>
     </row>
   </sheetData>
